--- a/data/nonACMGPLP_pLoF_allinfo_AA_Light.xlsx
+++ b/data/nonACMGPLP_pLoF_allinfo_AA_Light.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yvesgreatti/github/Variant-Effects/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E97199-D5E5-2349-BC2A-93B3E4F8D129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2EACA03-75FB-7743-A0DE-E376044F5066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="580" yWindow="9780" windowWidth="35840" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="5040" windowWidth="35840" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
